--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_313_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_313_R32.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5053</v>
+        <v>4.3765</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0907</v>
+        <v>4.0292</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4145</v>
+        <v>0.3473</v>
       </c>
       <c r="G2" t="n">
         <v>1.5986</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2984</v>
+        <v>1.1696</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7853</v>
+        <v>0.7237</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5131</v>
+        <v>0.4459</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8835</v>
+        <v>2.817</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4155</v>
+        <v>1.6514</v>
       </c>
       <c r="F3" t="n">
-        <v>1.468</v>
+        <v>1.1656</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0483</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3983</v>
+        <v>1.3317</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1379</v>
+        <v>0.3738</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2604</v>
+        <v>0.9579</v>
       </c>
       <c r="V3" t="n">
         <v>0.6778999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8986</v>
+        <v>1.6791</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4002</v>
+        <v>1.0463</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4984</v>
+        <v>0.6328</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4471</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5955</v>
+        <v>1.3761</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2977</v>
+        <v>0.9438</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2978</v>
+        <v>0.4323</v>
       </c>
       <c r="V4" t="n">
         <v>1.214</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.594</v>
+        <v>0.7866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1958</v>
+        <v>0.095</v>
       </c>
       <c r="G5" t="n">
         <v>1.0919</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0742</v>
+        <v>0.1661</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1336</v>
+        <v>0.0591</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2078</v>
+        <v>0.107</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5577</v>
+        <v>0.8683</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6508</v>
+        <v>0.9614</v>
       </c>
       <c r="F6" t="n">
         <v>-0.0931</v>
@@ -922,10 +922,10 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.224</v>
+        <v>0.5346</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2082</v>
+        <v>0.1024</v>
       </c>
       <c r="U6" t="n">
         <v>0.4323</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3738</v>
+        <v>0.8561</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1831</v>
+        <v>1.2586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5569</v>
+        <v>-0.4025</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7999000000000001</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3951</v>
+        <v>0.6976</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4049</v>
+        <v>-0.706</v>
       </c>
       <c r="J7" t="n">
-        <v>0.489</v>
+        <v>1.2072</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1344</v>
+        <v>2.1174</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3546</v>
+        <v>-0.9102</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3109</v>
+        <v>-1.2156</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2606</v>
+        <v>-1.4199</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0502</v>
+        <v>0.2042</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.89</v>
+        <v>0.6172</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6721</v>
+        <v>0.0514</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2179</v>
+        <v>0.5658</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MORRIS</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1579</v>
+        <v>0.6427</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0616</v>
+        <v>-0.1831</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0963</v>
+        <v>0.8257</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2106</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4214</v>
+        <v>0.3951</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2108</v>
+        <v>0.4049</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2857</v>
+        <v>0.489</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2857</v>
+        <v>0.1344</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.3546</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0751</v>
+        <v>0.3109</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1357</v>
+        <v>0.2606</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2108</v>
+        <v>0.0502</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0527</v>
+        <v>-0.6212</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>-0.6721</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1713</v>
+        <v>0.051</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0921</v>
+        <v>0.5296</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.289</v>
+        <v>-0.0531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3811</v>
+        <v>0.5827</v>
       </c>
       <c r="G9" t="n">
         <v>1.1867</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.007</v>
+        <v>0.4305</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1731</v>
+        <v>0.409</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1801</v>
+        <v>0.0215</v>
       </c>
       <c r="V9" t="n">
         <v>0.5361</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>M. MORRIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0607</v>
+        <v>0.0907</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4762</v>
+        <v>0.0616</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5369</v>
+        <v>0.029</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.2106</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6976</v>
+        <v>0.4214</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.706</v>
+        <v>-0.2108</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2072</v>
+        <v>0.2857</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1174</v>
+        <v>0.2857</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9102</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2156</v>
+        <v>-0.0751</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4199</v>
+        <v>0.1357</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2042</v>
+        <v>-0.2108</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2996</v>
+        <v>-0.1199</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.731</v>
+        <v>-0.224</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4314</v>
+        <v>0.1041</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.6643</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1321</v>
+        <v>0.0605</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6577</v>
+        <v>-0.7249</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8866000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1896</v>
+        <v>1.315</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5939</v>
+        <v>0.7866</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5957</v>
+        <v>0.5285</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3247</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0789</v>
+        <v>-2.2469</v>
       </c>
       <c r="E12" t="n">
         <v>-2.9237</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8448</v>
+        <v>0.6768</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2473</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.0718</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3949</v>
+        <v>0.2269</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3309</v>
+        <v>-2.4586</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.848</v>
+        <v>-3.0092</v>
       </c>
       <c r="F13" t="n">
-        <v>0.517</v>
+        <v>0.5506</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1293</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9581</v>
+        <v>0.8305</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6607</v>
+        <v>0.4995</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2974</v>
+        <v>0.331</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9984</v>
+        <v>7.371799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>3.313099999999999</v>
+        <v>3.686500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6851</v>
+        <v>3.685</v>
       </c>
       <c r="G14" t="n">
         <v>2.6141</v>
@@ -1516,7 +1516,7 @@
         <v>7.616299999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.002000000000001</v>
+        <v>-5.001999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>9.0318</v>
@@ -1528,7 +1528,7 @@
         <v>-6.7933</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.4178</v>
+        <v>-6.417799999999999</v>
       </c>
       <c r="N14" t="n">
         <v>-8.209200000000001</v>
@@ -1546,13 +1546,13 @@
         <v>12.7575</v>
       </c>
       <c r="S14" t="n">
-        <v>6.584999999999999</v>
+        <v>6.9584</v>
       </c>
       <c r="T14" t="n">
-        <v>2.381</v>
+        <v>2.7545</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2041</v>
+        <v>4.2042</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0411</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8514</v>
+        <v>4.7506</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0553</v>
+        <v>3.5271</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7961</v>
+        <v>1.2235</v>
       </c>
       <c r="G15" t="n">
         <v>1.306</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4752</v>
+        <v>-0.5759</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1791</v>
+        <v>-0.7073</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2961</v>
+        <v>0.1314</v>
       </c>
       <c r="V15" t="n">
         <v>2.3969</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5902</v>
+        <v>2.097</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9104</v>
+        <v>0.9679</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3202</v>
+        <v>1.1292</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0407</v>
+        <v>1.5288</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4249</v>
+        <v>0.5282</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6158</v>
+        <v>1.0005</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8031</v>
+        <v>1.522</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6995</v>
+        <v>1.4116</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.5026</v>
+        <v>0.1104</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2376</v>
+        <v>0.0067</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1244</v>
+        <v>-0.8834</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8868</v>
+        <v>0.8901</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5407999999999999</v>
+        <v>-0.2899</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3372</v>
+        <v>-0.5542</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7964</v>
+        <v>0.2642</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4665</v>
+        <v>0.3943</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5194</v>
+        <v>1.0899</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8499</v>
+        <v>0.613</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6695</v>
+        <v>0.4769</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5288</v>
+        <v>-2.0407</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5282</v>
+        <v>-1.4249</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0005</v>
+        <v>-0.6158</v>
       </c>
       <c r="J17" t="n">
-        <v>1.522</v>
+        <v>-0.8031</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4116</v>
+        <v>0.6995</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1104</v>
+        <v>-1.5026</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0067</v>
+        <v>-1.2376</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8834</v>
+        <v>-2.1244</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8901</v>
+        <v>0.8868</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8676</v>
+        <v>0.0404</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6721</v>
+        <v>0.0397</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1955</v>
+        <v>0.0007</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3943</v>
+        <v>1.4665</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.512</v>
+        <v>0.888</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1583</v>
+        <v>0.2762</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3537</v>
+        <v>0.6117</v>
       </c>
       <c r="G18" t="n">
         <v>0.6637</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5461</v>
+        <v>-0.17</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5149</v>
+        <v>-0.3969</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0312</v>
+        <v>0.2269</v>
       </c>
       <c r="V18" t="n">
         <v>0.3943</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3313</v>
+        <v>0.0503</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3066</v>
+        <v>-0.7784</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6379</v>
+        <v>0.8288</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4826</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4195</v>
+        <v>0.1386</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7117</v>
+        <v>0.2399</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2921</v>
+        <v>-0.1013</v>
       </c>
       <c r="V19" t="n">
         <v>0.3943</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0351</v>
+        <v>-1.3273</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4927</v>
+        <v>0.7286</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5278</v>
+        <v>-2.056</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2591</v>
@@ -2014,13 +2014,13 @@
         <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6316</v>
+        <v>-0.9238</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.963</v>
+        <v>-0.727</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6686</v>
+        <v>-0.1968</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2986</v>
+        <v>-1.9525</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0965</v>
+        <v>-2.1509</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2021</v>
+        <v>0.1984</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.735</v>
+        <v>-1.9457</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.929</v>
+        <v>-1.7249</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1941</v>
+        <v>-0.2208</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1376</v>
+        <v>-1.5732</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1008</v>
+        <v>-0.1478</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0368</v>
+        <v>-1.4255</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8726</v>
+        <v>-0.3725</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0299</v>
+        <v>-1.5771</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1573</v>
+        <v>1.2046</v>
       </c>
       <c r="P21" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.1598</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1349</v>
+        <v>-0.2388</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2161</v>
+        <v>-0.3457</v>
       </c>
       <c r="U21" t="n">
-        <v>0.351</v>
+        <v>0.107</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4665</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6766</v>
+        <v>-2.3322</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.201</v>
+        <v>-1.0965</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4756</v>
+        <v>-1.2357</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0629</v>
+        <v>-0.735</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5666</v>
+        <v>-0.929</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6295</v>
+        <v>0.1941</v>
       </c>
       <c r="J22" t="n">
-        <v>3.076</v>
+        <v>0.1376</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7043</v>
+        <v>0.1008</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3717</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0131</v>
+        <v>-0.8726</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.2709</v>
+        <v>-1.0299</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2578</v>
+        <v>0.1573</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-3.4793</v>
-      </c>
       <c r="R22" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4353</v>
+        <v>0.1013</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7978</v>
+        <v>-0.2161</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3624</v>
+        <v>0.3174</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1444</v>
+        <v>-1.4665</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9627</v>
+        <v>-2.3386</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3868</v>
+        <v>-0.9651</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5759</v>
+        <v>-1.3735</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9457</v>
+        <v>1.0629</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7249</v>
+        <v>-0.5666</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2208</v>
+        <v>1.6295</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5732</v>
+        <v>3.076</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1478</v>
+        <v>1.7043</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4255</v>
+        <v>1.3717</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3725</v>
+        <v>-2.0131</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5771</v>
+        <v>-2.2709</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2046</v>
+        <v>0.2578</v>
       </c>
       <c r="P23" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2489</v>
+        <v>-0.0973</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5816</v>
+        <v>-0.5619</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6673</v>
+        <v>0.4646</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8296</v>
+        <v>-3.9919</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.6969</v>
+        <v>-5.343</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8673</v>
+        <v>1.3512</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7124</v>
@@ -2326,13 +2326,13 @@
         <v>2.5515</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4756</v>
+        <v>-0.6379</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3285</v>
+        <v>-0.9746</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1472</v>
+        <v>0.3367</v>
       </c>
       <c r="V24" t="n">
         <v>0.6778999999999999</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9983</v>
+        <v>-3.0667</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2212</v>
+        <v>-4.2211</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.777099999999999</v>
+        <v>1.1545</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.614100000000001</v>
+        <v>-2.6141</v>
       </c>
       <c r="H25" t="n">
         <v>-7.6162</v>
@@ -2377,13 +2377,13 @@
         <v>5.0021</v>
       </c>
       <c r="J25" t="n">
-        <v>6.417799999999999</v>
+        <v>6.417800000000001</v>
       </c>
       <c r="K25" t="n">
         <v>8.209</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.791299999999999</v>
+        <v>-1.7913</v>
       </c>
       <c r="M25" t="n">
         <v>-9.0319</v>
@@ -2404,16 +2404,16 @@
         <v>13.9172</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.5851</v>
+        <v>-2.6533</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.2042</v>
+        <v>-4.2041</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.381</v>
+        <v>1.5508</v>
       </c>
       <c r="V25" t="n">
-        <v>1.0411</v>
+        <v>1.041099999999999</v>
       </c>
       <c r="W25" t="n">
         <v>6.3225</v>
